--- a/keemeds_commerce/master_data/output/images/Item_Image_Mapping.xlsx
+++ b/keemeds_commerce/master_data/output/images/Item_Image_Mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Item Image Mapping" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Image Mapping" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/files/item_images/med-001.webp</t>
+          <t>/files/item_images/MED-001-1.webp</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/files/item_images/med-002.webp</t>
+          <t>/files/item_images/MED-002-1.webp</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/files/item_images/med-003.webp</t>
+          <t>/files/item_images/MED-003-1.webp</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/files/item_images/med-004.webp</t>
+          <t>/files/item_images/MED-004-1.webp</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/files/item_images/med-005.webp</t>
+          <t>/files/item_images/MED-005-1.webp</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/files/item_images/med-006.webp</t>
+          <t>/files/item_images/MED-006-1.webp</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/files/item_images/med-007.webp</t>
+          <t>/files/item_images/MED-007-1.webp</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/files/item_images/med-008.webp</t>
+          <t>/files/item_images/MED-008-1.webp</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/files/item_images/med-009.webp</t>
+          <t>/files/item_images/MED-009-1.webp</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/files/item_images/med-010.webp</t>
+          <t>/files/item_images/MED-010-1.webp</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/files/item_images/med-011.webp</t>
+          <t>/files/item_images/MED-011-1.webp</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/files/item_images/med-012.webp</t>
+          <t>/files/item_images/MED-012-1.webp</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/files/item_images/med-013.webp</t>
+          <t>/files/item_images/MED-013-1.webp</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/files/item_images/med-014.webp</t>
+          <t>/files/item_images/MED-014-1.webp</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/files/item_images/med-015.webp</t>
+          <t>/files/item_images/MED-015-1.webp</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/files/item_images/med-016.webp</t>
+          <t>/files/item_images/MED-016-1.webp</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/files/item_images/med-017.webp</t>
+          <t>/files/item_images/MED-017-1.webp</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/files/item_images/med-018.webp</t>
+          <t>/files/item_images/MED-018-1.webp</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/files/item_images/med-019.webp</t>
+          <t>/files/item_images/MED-019-1.webp</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>/files/item_images/med-020.webp</t>
+          <t>/files/item_images/MED-020-1.webp</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>/files/item_images/med-021.webp</t>
+          <t>/files/item_images/MED-021-1.webp</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>/files/item_images/med-022.webp</t>
+          <t>/files/item_images/MED-022-1.webp</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>/files/item_images/med-023.webp</t>
+          <t>/files/item_images/MED-023-1.webp</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>/files/item_images/med-024.webp</t>
+          <t>/files/item_images/MED-024-1.webp</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>/files/item_images/med-025.webp</t>
+          <t>/files/item_images/MED-025-1.webp</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>/files/item_images/med-026.webp</t>
+          <t>/files/item_images/MED-026-1.webp</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>/files/item_images/med-027.webp</t>
+          <t>/files/item_images/MED-027-1.webp</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>/files/item_images/med-028.webp</t>
+          <t>/files/item_images/MED-028-1.webp</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>/files/item_images/med-029.webp</t>
+          <t>/files/item_images/MED-029-1.webp</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>/files/item_images/med-030.webp</t>
+          <t>/files/item_images/MED-030-1.webp</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>/files/item_images/med-031.webp</t>
+          <t>/files/item_images/MED-031-1.webp</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>/files/item_images/med-032.webp</t>
+          <t>/files/item_images/MED-032-1.webp</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>/files/item_images/med-033.webp</t>
+          <t>/files/item_images/MED-033-1.webp</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>/files/item_images/med-034.webp</t>
+          <t>/files/item_images/MED-034-1.webp</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>/files/item_images/med-035.webp</t>
+          <t>/files/item_images/MED-035-1.webp</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>/files/item_images/med-036.webp</t>
+          <t>/files/item_images/MED-036-1.webp</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>/files/item_images/med-037.webp</t>
+          <t>/files/item_images/MED-037-1.webp</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>/files/item_images/med-038.webp</t>
+          <t>/files/item_images/MED-038-1.webp</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>/files/item_images/med-039.webp</t>
+          <t>/files/item_images/MED-039-1.webp</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/files/item_images/med-040.webp</t>
+          <t>/files/item_images/MED-040-1.webp</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/files/item_images/med-041.webp</t>
+          <t>/files/item_images/MED-041-1.webp</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/files/item_images/med-042.webp</t>
+          <t>/files/item_images/MED-042-1.webp</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/files/item_images/med-043.webp</t>
+          <t>/files/item_images/MED-043-1.webp</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/files/item_images/med-044.webp</t>
+          <t>/files/item_images/MED-044-1.webp</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/files/item_images/med-045.webp</t>
+          <t>/files/item_images/MED-045-1.webp</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>/files/item_images/med-046.webp</t>
+          <t>/files/item_images/MED-046-1.webp</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>/files/item_images/med-047.webp</t>
+          <t>/files/item_images/MED-047-1.webp</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>/files/item_images/med-048.webp</t>
+          <t>/files/item_images/MED-048-1.webp</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>/files/item_images/med-049.webp</t>
+          <t>/files/item_images/MED-049-1.webp</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>/files/item_images/med-050.webp</t>
+          <t>/files/item_images/MED-050-1.webp</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>/files/item_images/med-051.webp</t>
+          <t>/files/item_images/MED-051-1.webp</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>/files/item_images/med-052.webp</t>
+          <t>/files/item_images/MED-052-1.webp</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>/files/item_images/med-053.webp</t>
+          <t>/files/item_images/MED-053-1.webp</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>/files/item_images/med-054.webp</t>
+          <t>/files/item_images/MED-054-1.webp</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>/files/item_images/med-055.webp</t>
+          <t>/files/item_images/MED-055-1.webp</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>/files/item_images/med-056.webp</t>
+          <t>/files/item_images/MED-056-1.webp</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>/files/item_images/med-057.webp</t>
+          <t>/files/item_images/MED-057-1.webp</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>/files/item_images/med-058.webp</t>
+          <t>/files/item_images/MED-058-1.webp</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>/files/item_images/med-059.webp</t>
+          <t>/files/item_images/MED-059-1.webp</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>/files/item_images/med-060.webp</t>
+          <t>/files/item_images/MED-060-1.webp</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>/files/item_images/med-061.webp</t>
+          <t>/files/item_images/MED-061-1.webp</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>/files/item_images/med-062.webp</t>
+          <t>/files/item_images/MED-062-1.webp</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>/files/item_images/med-063.webp</t>
+          <t>/files/item_images/MED-063-1.webp</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>/files/item_images/med-064.webp</t>
+          <t>/files/item_images/MED-064-1.webp</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>/files/item_images/med-065.webp</t>
+          <t>/files/item_images/MED-065-1.webp</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>/files/item_images/med-066.webp</t>
+          <t>/files/item_images/MED-066-1.webp</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>/files/item_images/med-067.webp</t>
+          <t>/files/item_images/MED-067-1.webp</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>/files/item_images/med-068.webp</t>
+          <t>/files/item_images/MED-068-1.webp</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>/files/item_images/med-069.webp</t>
+          <t>/files/item_images/MED-069-1.webp</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>/files/item_images/med-070.webp</t>
+          <t>/files/item_images/MED-070-1.webp</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>/files/item_images/med-071.webp</t>
+          <t>/files/item_images/MED-071-1.webp</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>/files/item_images/med-072.webp</t>
+          <t>/files/item_images/MED-072-1.webp</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>/files/item_images/med-073.webp</t>
+          <t>/files/item_images/MED-073-1.webp</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>/files/item_images/med-074.webp</t>
+          <t>/files/item_images/MED-074-1.webp</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>/files/item_images/med-075.webp</t>
+          <t>/files/item_images/MED-075-1.webp</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>/files/item_images/med-076.webp</t>
+          <t>/files/item_images/MED-076-1.webp</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>/files/item_images/med-077.webp</t>
+          <t>/files/item_images/MED-077-1.webp</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>/files/item_images/med-078.webp</t>
+          <t>/files/item_images/MED-078-1.webp</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>/files/item_images/med-079.webp</t>
+          <t>/files/item_images/MED-079-1.webp</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>/files/item_images/med-080.webp</t>
+          <t>/files/item_images/MED-080-1.webp</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>/files/item_images/med-081.webp</t>
+          <t>/files/item_images/MED-081-1.webp</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>/files/item_images/med-082.webp</t>
+          <t>/files/item_images/MED-082-1.webp</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>/files/item_images/med-083.webp</t>
+          <t>/files/item_images/MED-083-1.webp</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>/files/item_images/med-084.webp</t>
+          <t>/files/item_images/MED-084-1.webp</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>/files/item_images/med-085.webp</t>
+          <t>/files/item_images/MED-085-1.webp</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>/files/item_images/med-086.webp</t>
+          <t>/files/item_images/MED-086-1.webp</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>/files/item_images/med-087.webp</t>
+          <t>/files/item_images/MED-087-1.webp</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>/files/item_images/med-088.webp</t>
+          <t>/files/item_images/MED-088-1.webp</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>/files/item_images/med-089.webp</t>
+          <t>/files/item_images/MED-089-1.webp</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>/files/item_images/med-090.webp</t>
+          <t>/files/item_images/MED-090-1.webp</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>/files/item_images/med-091.webp</t>
+          <t>/files/item_images/MED-091-1.webp</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>/files/item_images/med-092.webp</t>
+          <t>/files/item_images/MED-092-1.webp</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>/files/item_images/med-093.webp</t>
+          <t>/files/item_images/MED-093-1.webp</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>/files/item_images/med-094.webp</t>
+          <t>/files/item_images/MED-094-1.webp</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>/files/item_images/med-095.webp</t>
+          <t>/files/item_images/MED-095-1.webp</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>/files/item_images/med-096.webp</t>
+          <t>/files/item_images/MED-096-1.webp</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>/files/item_images/med-097.webp</t>
+          <t>/files/item_images/MED-097-1.webp</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>/files/item_images/med-098.webp</t>
+          <t>/files/item_images/MED-098-1.webp</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>/files/item_images/med-099.webp</t>
+          <t>/files/item_images/MED-099-1.webp</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>/files/item_images/med-100.webp</t>
+          <t>/files/item_images/MED-100-1.webp</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>/files/item_images/med-101.webp</t>
+          <t>/files/item_images/MED-101-1.webp</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>/files/item_images/med-102.webp</t>
+          <t>/files/item_images/MED-102-1.webp</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>/files/item_images/med-103.webp</t>
+          <t>/files/item_images/MED-103-1.webp</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>/files/item_images/med-104.webp</t>
+          <t>/files/item_images/MED-104-1.webp</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>/files/item_images/med-105.webp</t>
+          <t>/files/item_images/MED-105-1.webp</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>/files/item_images/med-106.webp</t>
+          <t>/files/item_images/MED-106-1.webp</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>/files/item_images/med-107.webp</t>
+          <t>/files/item_images/MED-107-1.webp</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>/files/item_images/med-108.webp</t>
+          <t>/files/item_images/MED-108-1.webp</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>/files/item_images/med-109.webp</t>
+          <t>/files/item_images/MED-109-1.webp</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>/files/item_images/med-110.webp</t>
+          <t>/files/item_images/MED-110-1.webp</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>/files/item_images/med-111.webp</t>
+          <t>/files/item_images/MED-111-1.webp</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>/files/item_images/med-112.webp</t>
+          <t>/files/item_images/MED-112-1.webp</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>/files/item_images/med-113.webp</t>
+          <t>/files/item_images/MED-113-1.webp</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>/files/item_images/med-114.webp</t>
+          <t>/files/item_images/MED-114-1.webp</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>/files/item_images/med-115.webp</t>
+          <t>/files/item_images/MED-115-1.webp</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>/files/item_images/med-116.webp</t>
+          <t>/files/item_images/MED-116-1.webp</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>/files/item_images/med-117.webp</t>
+          <t>/files/item_images/MED-117-1.webp</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>/files/item_images/med-118.webp</t>
+          <t>/files/item_images/MED-118-1.webp</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>/files/item_images/med-119.webp</t>
+          <t>/files/item_images/MED-119-1.webp</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>/files/item_images/med-120.webp</t>
+          <t>/files/item_images/MED-120-1.webp</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>/files/item_images/med-121.webp</t>
+          <t>/files/item_images/MED-121-1.webp</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>/files/item_images/med-122.webp</t>
+          <t>/files/item_images/MED-122-1.webp</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>/files/item_images/med-123.webp</t>
+          <t>/files/item_images/MED-123-1.webp</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>/files/item_images/med-124.webp</t>
+          <t>/files/item_images/MED-124-1.webp</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>/files/item_images/med-125.webp</t>
+          <t>/files/item_images/MED-125-1.webp</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>/files/item_images/med-126.webp</t>
+          <t>/files/item_images/MED-126-1.webp</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>/files/item_images/med-127.webp</t>
+          <t>/files/item_images/MED-127-1.webp</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>/files/item_images/med-128.webp</t>
+          <t>/files/item_images/MED-128-1.webp</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>/files/item_images/med-129.webp</t>
+          <t>/files/item_images/MED-129-1.webp</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>/files/item_images/med-130.webp</t>
+          <t>/files/item_images/MED-130-1.webp</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>/files/item_images/med-131.webp</t>
+          <t>/files/item_images/MED-131-1.webp</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>/files/item_images/med-132.webp</t>
+          <t>/files/item_images/MED-132-1.webp</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>/files/item_images/med-133.webp</t>
+          <t>/files/item_images/MED-133-1.webp</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>/files/item_images/med-134.webp</t>
+          <t>/files/item_images/MED-134-1.webp</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>/files/item_images/med-135.webp</t>
+          <t>/files/item_images/MED-135-1.webp</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>/files/item_images/med-136.webp</t>
+          <t>/files/item_images/MED-136-1.webp</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>/files/item_images/med-137.webp</t>
+          <t>/files/item_images/MED-137-1.webp</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>/files/item_images/med-138.webp</t>
+          <t>/files/item_images/MED-138-1.webp</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>/files/item_images/med-139.webp</t>
+          <t>/files/item_images/MED-139-1.webp</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>/files/item_images/med-140.webp</t>
+          <t>/files/item_images/MED-140-1.webp</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>/files/item_images/med-141.webp</t>
+          <t>/files/item_images/MED-141-1.webp</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>/files/item_images/med-142.webp</t>
+          <t>/files/item_images/MED-142-1.webp</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>/files/item_images/med-143.webp</t>
+          <t>/files/item_images/MED-143-1.webp</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>/files/item_images/med-144.webp</t>
+          <t>/files/item_images/MED-144-1.webp</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>/files/item_images/med-145.webp</t>
+          <t>/files/item_images/MED-145-1.webp</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>/files/item_images/med-146.webp</t>
+          <t>/files/item_images/MED-146-1.webp</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>/files/item_images/med-147.webp</t>
+          <t>/files/item_images/MED-147-1.webp</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>/files/item_images/med-148.webp</t>
+          <t>/files/item_images/MED-148-1.webp</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>/files/item_images/med-149.webp</t>
+          <t>/files/item_images/MED-149-1.webp</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>/files/item_images/med-150.webp</t>
+          <t>/files/item_images/MED-150-1.webp</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>/files/item_images/med-151.webp</t>
+          <t>/files/item_images/MED-151-1.webp</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>/files/item_images/med-152.webp</t>
+          <t>/files/item_images/MED-152-1.webp</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>/files/item_images/med-153.webp</t>
+          <t>/files/item_images/MED-153-1.webp</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>/files/item_images/med-154.webp</t>
+          <t>/files/item_images/MED-154-1.webp</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>/files/item_images/med-155.webp</t>
+          <t>/files/item_images/MED-155-1.webp</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>/files/item_images/med-156.webp</t>
+          <t>/files/item_images/MED-156-1.webp</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>/files/item_images/med-157.webp</t>
+          <t>/files/item_images/MED-157-1.webp</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>/files/item_images/med-158.webp</t>
+          <t>/files/item_images/MED-158-1.webp</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>/files/item_images/med-159.webp</t>
+          <t>/files/item_images/MED-159-1.webp</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>/files/item_images/med-160.webp</t>
+          <t>/files/item_images/MED-160-1.webp</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>/files/item_images/med-161.webp</t>
+          <t>/files/item_images/MED-161-1.webp</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>/files/item_images/med-162.webp</t>
+          <t>/files/item_images/MED-162-1.webp</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>/files/item_images/med-163.webp</t>
+          <t>/files/item_images/MED-163-1.webp</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>/files/item_images/med-164.webp</t>
+          <t>/files/item_images/MED-164-1.webp</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>/files/item_images/med-165.webp</t>
+          <t>/files/item_images/MED-165-1.webp</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>/files/item_images/med-166.webp</t>
+          <t>/files/item_images/MED-166-1.webp</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>/files/item_images/med-167.webp</t>
+          <t>/files/item_images/MED-167-1.webp</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>/files/item_images/med-168.webp</t>
+          <t>/files/item_images/MED-168-1.webp</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>/files/item_images/med-169.webp</t>
+          <t>/files/item_images/MED-169-1.webp</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>/files/item_images/med-170.webp</t>
+          <t>/files/item_images/MED-170-1.webp</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>/files/item_images/med-171.webp</t>
+          <t>/files/item_images/MED-171-1.webp</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>/files/item_images/med-172.webp</t>
+          <t>/files/item_images/MED-172-1.webp</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>/files/item_images/med-173.webp</t>
+          <t>/files/item_images/MED-173-1.webp</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>/files/item_images/med-174.webp</t>
+          <t>/files/item_images/MED-174-1.webp</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>/files/item_images/med-175.webp</t>
+          <t>/files/item_images/MED-175-1.webp</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>/files/item_images/med-176.webp</t>
+          <t>/files/item_images/MED-176-1.webp</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>/files/item_images/med-177.webp</t>
+          <t>/files/item_images/MED-177-1.webp</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>/files/item_images/med-178.webp</t>
+          <t>/files/item_images/MED-178-1.webp</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>/files/item_images/med-179.webp</t>
+          <t>/files/item_images/MED-179-1.webp</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>/files/item_images/med-180.webp</t>
+          <t>/files/item_images/MED-180-1.webp</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>/files/item_images/med-181.webp</t>
+          <t>/files/item_images/MED-181-1.webp</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>/files/item_images/med-182.webp</t>
+          <t>/files/item_images/MED-182-1.webp</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>/files/item_images/med-183.webp</t>
+          <t>/files/item_images/MED-183-1.webp</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>/files/item_images/med-184.webp</t>
+          <t>/files/item_images/MED-184-1.webp</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>/files/item_images/med-185.webp</t>
+          <t>/files/item_images/MED-185-1.webp</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>/files/item_images/med-186.webp</t>
+          <t>/files/item_images/MED-186-1.webp</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>/files/item_images/med-187.webp</t>
+          <t>/files/item_images/MED-187-1.webp</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>/files/item_images/med-188.webp</t>
+          <t>/files/item_images/MED-188-1.webp</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>/files/item_images/med-189.webp</t>
+          <t>/files/item_images/MED-189-1.webp</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>/files/item_images/med-190.webp</t>
+          <t>/files/item_images/MED-190-1.webp</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>/files/item_images/med-191.webp</t>
+          <t>/files/item_images/MED-191-1.webp</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>/files/item_images/med-192.webp</t>
+          <t>/files/item_images/MED-192-1.webp</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>/files/item_images/med-193.webp</t>
+          <t>/files/item_images/MED-193-1.webp</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>/files/item_images/med-194.webp</t>
+          <t>/files/item_images/MED-194-1.webp</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>/files/item_images/med-195.webp</t>
+          <t>/files/item_images/MED-195-1.webp</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>/files/item_images/med-196.webp</t>
+          <t>/files/item_images/MED-196-1.webp</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>/files/item_images/med-197.webp</t>
+          <t>/files/item_images/MED-197-1.webp</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>/files/item_images/med-198.webp</t>
+          <t>/files/item_images/MED-198-1.webp</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>/files/item_images/med-199.webp</t>
+          <t>/files/item_images/MED-199-1.webp</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>/files/item_images/med-200.webp</t>
+          <t>/files/item_images/MED-200-1.webp</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>/files/item_images/med-201.webp</t>
+          <t>/files/item_images/MED-201-1.webp</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>/files/item_images/med-202.webp</t>
+          <t>/files/item_images/MED-202-1.webp</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>/files/item_images/med-203.webp</t>
+          <t>/files/item_images/MED-203-1.webp</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>/files/item_images/med-204.webp</t>
+          <t>/files/item_images/MED-204-1.webp</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>/files/item_images/med-205.webp</t>
+          <t>/files/item_images/MED-205-1.webp</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>/files/item_images/med-206.webp</t>
+          <t>/files/item_images/MED-206-1.webp</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>/files/item_images/med-207.webp</t>
+          <t>/files/item_images/MED-207-1.webp</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>/files/item_images/med-208.webp</t>
+          <t>/files/item_images/MED-208-1.webp</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>/files/item_images/med-209.webp</t>
+          <t>/files/item_images/MED-209-1.webp</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>/files/item_images/med-210.webp</t>
+          <t>/files/item_images/MED-210-1.webp</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>/files/item_images/med-211.webp</t>
+          <t>/files/item_images/MED-211-1.webp</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>/files/item_images/med-212.webp</t>
+          <t>/files/item_images/MED-212-1.webp</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>/files/item_images/med-213.webp</t>
+          <t>/files/item_images/MED-213-1.webp</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>/files/item_images/med-214.webp</t>
+          <t>/files/item_images/MED-214-1.webp</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>/files/item_images/med-215.webp</t>
+          <t>/files/item_images/MED-215-1.webp</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>/files/item_images/med-216.webp</t>
+          <t>/files/item_images/MED-216-1.webp</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>/files/item_images/med-217.webp</t>
+          <t>/files/item_images/MED-217-1.webp</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>/files/item_images/med-218.webp</t>
+          <t>/files/item_images/MED-218-1.webp</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>/files/item_images/med-219.webp</t>
+          <t>/files/item_images/MED-219-1.webp</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>/files/item_images/med-220.webp</t>
+          <t>/files/item_images/MED-220-1.webp</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>/files/item_images/med-221.webp</t>
+          <t>/files/item_images/MED-221-1.webp</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>/files/item_images/med-222.webp</t>
+          <t>/files/item_images/MED-222-1.webp</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>/files/item_images/med-223.webp</t>
+          <t>/files/item_images/MED-223-1.webp</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>/files/item_images/med-224.webp</t>
+          <t>/files/item_images/MED-224-1.webp</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>/files/item_images/med-225.webp</t>
+          <t>/files/item_images/MED-225-1.webp</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>/files/item_images/med-226.webp</t>
+          <t>/files/item_images/MED-226-1.webp</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>/files/item_images/med-227.webp</t>
+          <t>/files/item_images/MED-227-1.webp</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>/files/item_images/med-228.webp</t>
+          <t>/files/item_images/MED-228-1.webp</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>/files/item_images/med-229.webp</t>
+          <t>/files/item_images/MED-229-1.webp</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>/files/item_images/med-230.webp</t>
+          <t>/files/item_images/MED-230-1.webp</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>/files/item_images/med-231.webp</t>
+          <t>/files/item_images/MED-231-1.webp</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>/files/item_images/med-232.webp</t>
+          <t>/files/item_images/MED-232-1.webp</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>/files/item_images/med-233.webp</t>
+          <t>/files/item_images/MED-233-1.webp</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>/files/item_images/med-234.webp</t>
+          <t>/files/item_images/MED-234-1.webp</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>/files/item_images/med-235.webp</t>
+          <t>/files/item_images/MED-235-1.webp</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>/files/item_images/med-236.webp</t>
+          <t>/files/item_images/MED-236-1.webp</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>/files/item_images/med-237.webp</t>
+          <t>/files/item_images/MED-237-1.webp</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>/files/item_images/med-238.webp</t>
+          <t>/files/item_images/MED-238-1.webp</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>/files/item_images/med-239.webp</t>
+          <t>/files/item_images/MED-239-1.webp</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>/files/item_images/med-240.webp</t>
+          <t>/files/item_images/MED-240-1.webp</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>/files/item_images/med-241.webp</t>
+          <t>/files/item_images/MED-241-1.webp</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>/files/item_images/med-242.webp</t>
+          <t>/files/item_images/MED-242-1.webp</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>/files/item_images/med-243.webp</t>
+          <t>/files/item_images/MED-243-1.webp</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>/files/item_images/med-244.webp</t>
+          <t>/files/item_images/MED-244-1.webp</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>/files/item_images/med-245.webp</t>
+          <t>/files/item_images/MED-245-1.webp</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>/files/item_images/med-246.webp</t>
+          <t>/files/item_images/MED-246-1.webp</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>/files/item_images/med-247.webp</t>
+          <t>/files/item_images/MED-247-1.webp</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>/files/item_images/med-248.webp</t>
+          <t>/files/item_images/MED-248-1.webp</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>/files/item_images/med-249.webp</t>
+          <t>/files/item_images/MED-249-1.webp</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>/files/item_images/med-250.webp</t>
+          <t>/files/item_images/MED-250-1.webp</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>/files/item_images/med-251.webp</t>
+          <t>/files/item_images/MED-251-1.webp</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>/files/item_images/med-252.webp</t>
+          <t>/files/item_images/MED-252-1.webp</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>/files/item_images/med-253.webp</t>
+          <t>/files/item_images/MED-253-1.webp</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>/files/item_images/med-254.webp</t>
+          <t>/files/item_images/MED-254-1.webp</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>/files/item_images/med-255.webp</t>
+          <t>/files/item_images/MED-255-1.webp</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>/files/item_images/med-256.webp</t>
+          <t>/files/item_images/MED-256-1.webp</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>/files/item_images/med-257.webp</t>
+          <t>/files/item_images/MED-257-1.webp</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>/files/item_images/med-258.webp</t>
+          <t>/files/item_images/MED-258-1.webp</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>/files/item_images/med-259.webp</t>
+          <t>/files/item_images/MED-259-1.webp</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>/files/item_images/med-260.webp</t>
+          <t>/files/item_images/MED-260-1.webp</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>/files/item_images/med-261.webp</t>
+          <t>/files/item_images/MED-261-1.webp</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>/files/item_images/med-262.webp</t>
+          <t>/files/item_images/MED-262-1.webp</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>/files/item_images/med-263.webp</t>
+          <t>/files/item_images/MED-263-1.webp</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>/files/item_images/med-264.webp</t>
+          <t>/files/item_images/MED-264-1.webp</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>/files/item_images/med-265.webp</t>
+          <t>/files/item_images/MED-265-1.webp</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>/files/item_images/med-266.webp</t>
+          <t>/files/item_images/MED-266-1.webp</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>/files/item_images/med-267.webp</t>
+          <t>/files/item_images/MED-267-1.webp</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>/files/item_images/med-268.webp</t>
+          <t>/files/item_images/MED-268-1.webp</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>/files/item_images/med-269.webp</t>
+          <t>/files/item_images/MED-269-1.webp</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>/files/item_images/med-270.webp</t>
+          <t>/files/item_images/MED-270-1.webp</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>/files/item_images/med-271.webp</t>
+          <t>/files/item_images/MED-271-1.webp</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>/files/item_images/med-272.webp</t>
+          <t>/files/item_images/MED-272-1.webp</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>/files/item_images/med-273.webp</t>
+          <t>/files/item_images/MED-273-1.webp</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>/files/item_images/med-274.webp</t>
+          <t>/files/item_images/MED-274-1.webp</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>/files/item_images/med-275.webp</t>
+          <t>/files/item_images/MED-275-1.webp</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>/files/item_images/med-276.webp</t>
+          <t>/files/item_images/MED-276-1.webp</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>/files/item_images/med-277.webp</t>
+          <t>/files/item_images/MED-277-1.webp</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>/files/item_images/med-278.webp</t>
+          <t>/files/item_images/MED-278-1.webp</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>/files/item_images/med-279.webp</t>
+          <t>/files/item_images/MED-279-1.webp</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>/files/item_images/med-280.webp</t>
+          <t>/files/item_images/MED-280-1.webp</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>/files/item_images/med-281.webp</t>
+          <t>/files/item_images/MED-281-1.webp</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>/files/item_images/med-282.webp</t>
+          <t>/files/item_images/MED-282-1.webp</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>/files/item_images/med-283.webp</t>
+          <t>/files/item_images/MED-283-1.webp</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>/files/item_images/med-284.webp</t>
+          <t>/files/item_images/MED-284-1.webp</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>/files/item_images/med-285.webp</t>
+          <t>/files/item_images/MED-285-1.webp</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>/files/item_images/med-286.webp</t>
+          <t>/files/item_images/MED-286-1.webp</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>/files/item_images/med-287.webp</t>
+          <t>/files/item_images/MED-287-1.webp</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>/files/item_images/med-288.webp</t>
+          <t>/files/item_images/MED-288-1.webp</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>/files/item_images/med-289.webp</t>
+          <t>/files/item_images/MED-289-1.webp</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>/files/item_images/med-290.webp</t>
+          <t>/files/item_images/MED-290-1.webp</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>/files/item_images/med-291.webp</t>
+          <t>/files/item_images/MED-291-1.webp</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>/files/item_images/med-292.webp</t>
+          <t>/files/item_images/MED-292-1.webp</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>/files/item_images/med-293.webp</t>
+          <t>/files/item_images/MED-293-1.webp</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>/files/item_images/med-294.webp</t>
+          <t>/files/item_images/MED-294-1.webp</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>/files/item_images/med-295.webp</t>
+          <t>/files/item_images/MED-295-1.webp</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>/files/item_images/med-296.webp</t>
+          <t>/files/item_images/MED-296-1.webp</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>/files/item_images/med-297.webp</t>
+          <t>/files/item_images/MED-297-1.webp</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>/files/item_images/med-298.webp</t>
+          <t>/files/item_images/MED-298-1.webp</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>/files/item_images/med-299.webp</t>
+          <t>/files/item_images/MED-299-1.webp</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>/files/item_images/med-300.webp</t>
+          <t>/files/item_images/MED-300-1.webp</t>
         </is>
       </c>
     </row>
